--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,12 +456,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,29 +476,29 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -513,29 +513,29 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -545,29 +545,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -604,207 +604,207 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -814,182 +814,182 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1.5053</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.5051</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -999,135 +999,135 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.5053</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1.5236</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>1.6</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1137,44 +1137,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1189,88 +1189,88 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>1.64</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1295,66 +1295,66 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1374,145 +1374,145 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>1.6</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1522,56 +1522,56 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1591,246 +1591,246 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1845,29 +1845,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1877,66 +1877,66 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1961,81 +1961,155 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,12 +456,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,24 +476,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -523,19 +523,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -545,34 +545,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -582,12 +582,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -597,14 +597,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -678,101 +678,101 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -782,39 +782,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -826,229 +826,229 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1.5053</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>1.62</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>1.5051</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1073,24 +1073,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1100,17 +1100,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1122,17 +1122,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1142,71 +1142,71 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1226,19 +1226,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1263,130 +1263,130 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>1.55</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1406,29 +1406,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1455,54 +1455,54 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1512,24 +1512,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1544,17 +1544,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1566,64 +1566,64 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1633,24 +1633,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1660,49 +1660,49 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1714,96 +1714,96 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1813,61 +1813,61 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1882,29 +1882,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1936,12 +1936,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1951,29 +1951,29 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1998,19 +1998,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2035,74 +2035,98 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -2111,6 +2135,19 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,7 +476,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -493,12 +493,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -513,24 +513,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -560,19 +560,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -582,34 +582,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -619,12 +619,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -634,14 +634,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -715,101 +715,101 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -819,39 +819,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -863,229 +863,229 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1.5053</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>1.62</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>1.5051</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1110,24 +1110,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1159,17 +1159,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1179,71 +1179,71 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1263,19 +1263,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1300,130 +1300,130 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>1.55</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1443,29 +1443,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1492,54 +1492,54 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1549,24 +1549,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1581,17 +1581,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1603,64 +1603,64 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1697,49 +1697,49 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1751,96 +1751,96 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1850,61 +1850,61 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1919,29 +1919,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1973,12 +1973,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1988,29 +1988,29 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2035,19 +2035,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2072,74 +2072,98 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -2148,6 +2172,19 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,34 +476,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -530,12 +530,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -550,24 +550,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -597,19 +597,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -619,34 +619,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -656,12 +656,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -752,101 +752,101 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -856,39 +856,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -900,229 +900,229 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1.5053</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>1.62</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>1.5051</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1147,24 +1147,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1174,17 +1174,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1196,17 +1196,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1216,71 +1216,71 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1300,19 +1300,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1337,130 +1337,130 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>1.55</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1480,29 +1480,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1529,54 +1529,54 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1586,24 +1586,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1618,17 +1618,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1640,64 +1640,64 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1707,24 +1707,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1734,49 +1734,49 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1788,96 +1788,96 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1887,61 +1887,61 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1956,29 +1956,29 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2010,12 +2010,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2025,29 +2025,29 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2072,19 +2072,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2109,74 +2109,98 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -2185,6 +2209,19 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,24 +476,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,29 +513,29 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -550,34 +550,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -592,24 +592,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -619,34 +619,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -661,29 +661,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -698,29 +698,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -730,29 +730,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -789,207 +789,207 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -999,182 +999,182 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>1.5053</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.5051</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1184,135 +1184,135 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.5053</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1.5236</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>1.6</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1322,44 +1322,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1374,88 +1374,88 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>1.64</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1480,66 +1480,66 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1559,145 +1559,145 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>1.6</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1707,56 +1707,56 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1776,246 +1776,246 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2030,29 +2030,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2062,66 +2062,66 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2146,81 +2146,155 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -466,17 +466,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -486,24 +486,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,29 +513,29 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -555,29 +555,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -587,34 +587,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -641,12 +641,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -661,24 +661,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -708,19 +708,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -730,34 +730,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -782,14 +782,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -826,7 +826,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -863,101 +863,101 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -967,39 +967,39 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1011,229 +1011,229 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1.5053</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>1.62</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1.5051</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1307,17 +1307,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1327,71 +1327,71 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1411,19 +1411,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1448,130 +1448,130 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>1.55</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1591,29 +1591,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1640,54 +1640,54 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1729,17 +1729,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1751,64 +1751,64 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1818,24 +1818,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1845,49 +1845,49 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1899,96 +1899,96 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1998,61 +1998,61 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2067,29 +2067,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2121,12 +2121,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2136,29 +2136,29 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2183,19 +2183,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2220,74 +2220,98 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -2296,6 +2320,19 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,22 +456,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -481,19 +481,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -503,34 +503,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -540,12 +540,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -555,34 +555,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -592,29 +592,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -629,24 +629,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -661,29 +661,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -698,39 +698,39 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -740,24 +740,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -772,29 +772,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -804,34 +804,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -883,192 +883,192 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1078,140 +1078,140 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1221,246 +1221,246 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.5051</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5053</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1470,150 +1470,150 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1628,140 +1628,140 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1771,81 +1771,81 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1855,108 +1855,108 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1966,372 +1966,483 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -481,56 +481,56 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -545,44 +545,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -592,19 +592,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -614,34 +614,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -666,34 +666,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -703,29 +703,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -740,24 +740,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -772,29 +772,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -809,39 +809,39 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -851,24 +851,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -883,29 +883,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -915,34 +915,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -957,29 +957,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -994,192 +994,192 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1189,140 +1189,140 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1332,246 +1332,246 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.5051</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5053</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1581,150 +1581,150 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1739,140 +1739,140 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1882,81 +1882,81 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1966,108 +1966,108 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2077,372 +2077,483 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -493,17 +493,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,12 +513,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -530,17 +530,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -597,19 +597,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -634,88 +634,88 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -725,17 +725,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -745,24 +745,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -772,29 +772,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -814,29 +814,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -846,34 +846,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -900,12 +900,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -920,24 +920,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -967,19 +967,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -989,34 +989,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1041,14 +1041,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1085,7 +1085,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1122,101 +1122,101 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1226,39 +1226,39 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1270,229 +1270,229 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1.5053</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>1.62</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>1.5051</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1517,24 +1517,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1544,17 +1544,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1566,17 +1566,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1586,71 +1586,71 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1670,19 +1670,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1707,130 +1707,130 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>1.55</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1850,29 +1850,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1899,54 +1899,54 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1956,24 +1956,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1988,17 +1988,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2010,64 +2010,64 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2077,24 +2077,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2104,49 +2104,49 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2158,96 +2158,96 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2257,61 +2257,61 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2326,29 +2326,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2380,12 +2380,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2395,29 +2395,29 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2442,19 +2442,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2479,74 +2479,98 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -2555,6 +2579,19 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,128 +456,128 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>1.44</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.311</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -604,17 +604,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -629,56 +629,56 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -693,44 +693,44 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -740,19 +740,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,34 +762,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -814,34 +814,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -851,29 +851,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -888,24 +888,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -920,29 +920,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -957,39 +957,39 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -999,24 +999,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1031,29 +1031,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1063,34 +1063,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1105,29 +1105,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1142,192 +1142,192 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1337,140 +1337,140 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1480,246 +1480,246 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.5051</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5053</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1729,150 +1729,150 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1887,140 +1887,140 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2030,81 +2030,81 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2114,108 +2114,108 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2225,372 +2225,483 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,24 +456,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>1.27</t>
@@ -481,56 +481,56 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>1.42</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -540,17 +540,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -560,19 +560,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -582,39 +582,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.311</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -641,17 +641,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -745,19 +745,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -782,88 +782,88 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -893,24 +893,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -920,29 +920,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -962,29 +962,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -994,34 +994,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1048,12 +1048,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1068,24 +1068,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1115,19 +1115,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1137,34 +1137,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1189,14 +1189,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1270,101 +1270,101 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1374,39 +1374,39 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1418,229 +1418,229 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1.5053</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>1.62</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1.5051</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1665,24 +1665,24 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1692,17 +1692,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1714,17 +1714,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1734,71 +1734,71 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1818,19 +1818,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1855,130 +1855,130 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>1.55</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1998,29 +1998,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2047,54 +2047,54 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2104,24 +2104,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2158,64 +2158,64 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2225,24 +2225,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2252,49 +2252,49 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2306,96 +2306,96 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2405,61 +2405,61 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2474,29 +2474,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2528,12 +2528,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2543,29 +2543,29 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2590,19 +2590,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2627,74 +2627,98 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -2703,6 +2727,19 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,61 +456,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>1.4</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>1.27</t>
@@ -518,56 +518,56 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>1.42</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -577,17 +577,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -597,19 +597,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -619,39 +619,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.311</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -715,17 +715,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -752,7 +752,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -782,19 +782,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -819,88 +819,88 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -910,17 +910,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -930,24 +930,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -957,29 +957,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -999,29 +999,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1031,34 +1031,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1085,12 +1085,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1105,24 +1105,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1152,19 +1152,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1174,34 +1174,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1226,14 +1226,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1307,101 +1307,101 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1411,39 +1411,39 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1455,229 +1455,229 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1.5053</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>1.62</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1.5051</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1729,17 +1729,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1751,17 +1751,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1771,71 +1771,71 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1855,19 +1855,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1892,130 +1892,130 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>1.55</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2035,29 +2035,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2084,54 +2084,54 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2173,17 +2173,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2195,64 +2195,64 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2262,24 +2262,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2289,49 +2289,49 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2343,96 +2343,96 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2442,61 +2442,61 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2511,29 +2511,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2565,12 +2565,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2580,29 +2580,29 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2627,19 +2627,19 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2664,74 +2664,98 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -2740,6 +2764,19 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,12 +456,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,78 +476,78 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>1.35</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1.4</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>1.27</t>
@@ -555,56 +555,56 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>1.42</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -614,17 +614,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -634,19 +634,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -656,39 +656,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.311</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -715,17 +715,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -752,17 +752,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -819,19 +819,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -856,88 +856,88 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -967,24 +967,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -994,29 +994,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1036,29 +1036,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1068,34 +1068,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1122,12 +1122,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1142,24 +1142,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1211,34 +1211,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1263,14 +1263,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1344,101 +1344,101 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1448,39 +1448,39 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1492,229 +1492,229 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1.5053</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>1.62</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1.5051</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1739,24 +1739,24 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1788,17 +1788,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1808,71 +1808,71 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1892,19 +1892,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1929,130 +1929,130 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>1.55</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2072,29 +2072,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2121,54 +2121,54 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2178,24 +2178,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2210,17 +2210,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2232,64 +2232,64 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2299,24 +2299,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2326,49 +2326,49 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2380,96 +2380,96 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2479,61 +2479,61 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2548,29 +2548,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2602,12 +2602,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2617,29 +2617,29 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2664,19 +2664,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2701,74 +2701,98 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -2777,6 +2801,19 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,49 +456,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07 Apr 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.2992</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -508,261 +508,261 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>1.35</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>1.35</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>1.44</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.311</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -789,17 +789,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -826,17 +826,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -893,14 +893,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -925,19 +925,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -962,71 +962,71 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1036,29 +1036,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1068,24 +1068,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1105,29 +1105,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1142,34 +1142,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1211,34 +1211,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1253,29 +1253,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1290,29 +1290,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1322,29 +1322,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,207 +1381,207 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1591,182 +1591,182 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1.5053</t>
-        </is>
-      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.5051</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1776,135 +1776,135 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.5053</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1.5236</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>1.6</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1914,44 +1914,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1966,88 +1966,88 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>1.64</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2072,66 +2072,66 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2151,145 +2151,145 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>1.6</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2299,56 +2299,56 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2368,246 +2368,246 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2622,29 +2622,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2654,66 +2654,66 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2723,12 +2723,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2738,81 +2738,155 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,12 +456,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.2992</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,29 +481,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.2992</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -523,14 +523,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07 Apr 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -567,12 +567,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,78 +587,78 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>1.35</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>1.4</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>1.27</t>
@@ -666,56 +666,56 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>1.42</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -725,17 +725,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -745,19 +745,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -767,39 +767,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.311</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -826,17 +826,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -863,17 +863,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -930,19 +930,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -967,88 +967,88 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1078,24 +1078,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1105,29 +1105,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1147,29 +1147,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1179,34 +1179,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1233,12 +1233,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1253,24 +1253,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1300,19 +1300,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1322,34 +1322,34 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1374,14 +1374,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1455,101 +1455,101 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1559,39 +1559,39 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1603,229 +1603,229 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1.5053</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>1.62</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1.5051</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1850,24 +1850,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1877,17 +1877,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1919,71 +1919,71 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2003,19 +2003,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2040,130 +2040,130 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>1.55</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2183,29 +2183,29 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2232,54 +2232,54 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2289,24 +2289,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2343,64 +2343,64 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2410,24 +2410,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2437,49 +2437,49 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2491,96 +2491,96 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2590,61 +2590,61 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2659,29 +2659,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2713,12 +2713,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3456</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2728,29 +2728,29 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2775,19 +2775,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2812,74 +2812,98 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -2888,6 +2912,19 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10 Apr 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -481,24 +481,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.2992</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -523,24 +523,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -567,32 +567,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07 Apr 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -604,22 +604,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -641,340 +641,340 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.2992</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.311</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -999,34 +999,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1036,71 +1036,71 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>1.5</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1110,19 +1110,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1132,49 +1132,49 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>1.52</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1184,19 +1184,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1206,81 +1206,81 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1300,19 +1300,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1322,29 +1322,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1369,61 +1369,61 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1433,34 +1433,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1485,236 +1485,236 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>1.45</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1739,56 +1739,56 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1798,12 +1798,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1813,71 +1813,71 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.5051</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1887,61 +1887,61 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1951,113 +1951,113 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5053</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.5051</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>1.63</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2067,293 +2067,293 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>1.6</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2363,49 +2363,49 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2417,123 +2417,123 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2543,39 +2543,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2585,49 +2585,49 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2639,27 +2639,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2669,261 +2669,446 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>08 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1.3456</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>07 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,192 +456,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16 Apr 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.3131</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3092</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13 Apr 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10 Apr 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -651,71 +651,71 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>15 May 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.2992</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -725,1243 +725,1243 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07 Apr 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>1.29</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.31</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>11 May 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>09 May 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.3758</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.3758</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>08 May 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>07 May 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>06 May 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>30 Apr 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>29 Apr 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3732</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>27 Apr 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.3502</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>24 Apr 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>23 Apr 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>22 Apr 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>21 Apr 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>20 Apr 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.2992</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>1.35</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>1.35</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.311</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1973,244 +1973,244 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.5051</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2220,34 +2220,34 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2257,377 +2257,377 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2639,54 +2639,54 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2696,71 +2696,71 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>1.55</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2770,224 +2770,224 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
           <t>1.4</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5053</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2997,118 +2997,1006 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>04 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>03 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>02 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>30 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>29 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>28 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>27 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>26 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>23 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>22 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>21 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1.4173</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>19 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>16 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>15 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>14 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>13 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>12 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>09 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>08 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1.3456</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>07 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr">
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,365 +456,365 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>16 Jun 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>15 Jun 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>12 Jun 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.3131</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>11 Jun 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.443</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.3092</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>10 Jun 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>09 Jun 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15 May 2026</t>
+          <t>08 Jun 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>05 Jun 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>1.37</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1.3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>04 Jun 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>03 Jun 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -826,32 +826,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11 May 2026</t>
+          <t>02 Jun 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -863,54 +863,54 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09 May 2026</t>
+          <t>01 Jun 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.3758</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.3758</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08 May 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -937,44 +937,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07 May 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.3577</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06 May 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -984,76 +984,76 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.3639</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30 Apr 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.3727</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.394</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>29 Apr 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1068,209 +1068,209 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.3732</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>27 Apr 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1.3131</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>1.33</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>1.3502</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>24 Apr 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3092</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>23 Apr 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>22 Apr 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>1.31</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>21 Apr 2026</t>
+          <t>15 May 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1280,71 +1280,71 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20 Apr 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1354,34 +1354,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>1.31</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16 Apr 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1391,22 +1391,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>11 May 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1428,133 +1428,133 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>09 May 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.3758</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3758</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13 Apr 2026</t>
+          <t>08 May 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>1.36</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10 Apr 2026</t>
+          <t>07 May 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1566,32 +1566,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>06 May 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.2992</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1603,98 +1603,98 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>30 Apr 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07 Apr 2026</t>
+          <t>29 Apr 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>1.24</t>
@@ -1702,722 +1702,722 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3732</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>27 Apr 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3502</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>24 Apr 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>23 Apr 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>22 Apr 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>21 Apr 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>20 Apr 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>1.2992</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>1.41</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2427,44 +2427,44 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.311</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2474,34 +2474,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2511,29 +2511,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2558,362 +2558,362 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2923,584 +2923,584 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1.5051</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1.5236</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
           <t>1.4</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
           <t>1.5</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5053</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3510,71 +3510,71 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3584,71 +3584,71 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3658,123 +3658,123 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>1.57</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3786,217 +3786,809 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>23 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>22 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>21 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1.4173</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>19 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>16 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>15 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>14 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>13 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>12 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>09 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>08 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1.3456</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>07 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr">
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,562 +456,562 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16 Jun 2026</t>
+          <t>26 Jun 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>1.45</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15 Jun 2026</t>
+          <t>25 Jun 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12 Jun 2026</t>
+          <t>24 Jun 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.5461</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11 Jun 2026</t>
+          <t>23 Jun 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10 Jun 2026</t>
+          <t>22 Jun 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09 Jun 2026</t>
+          <t>18 Jun 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08 Jun 2026</t>
+          <t>17 Jun 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05 Jun 2026</t>
+          <t>16 Jun 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>04 Jun 2026</t>
+          <t>15 Jun 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03 Jun 2026</t>
+          <t>12 Jun 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02 Jun 2026</t>
+          <t>11 Jun 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.443</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01 Jun 2026</t>
+          <t>10 Jun 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>29 May 2026</t>
+          <t>09 Jun 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>08 Jun 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>1.38</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1.3577</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>05 Jun 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>1.3639</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>04 Jun 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1021,49 +1021,49 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.3727</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>03 Jun 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1073,36 +1073,36 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>02 Jun 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>1.32</t>
@@ -1115,19 +1115,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>01 Jun 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1142,71 +1142,71 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.3131</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>1.36</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>1.3092</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1216,34 +1216,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.3577</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1253,160 +1253,160 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.3639</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3727</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.394</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>1.37</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1.3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3131</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1418,64 +1418,64 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>11 May 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3092</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09 May 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.3758</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1485,315 +1485,315 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.3758</t>
+          <t>1.31</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08 May 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.31</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07 May 2026</t>
+          <t>15 May 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06 May 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>30 Apr 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.31</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>29 Apr 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>11 May 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.3732</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>27 Apr 2026</t>
+          <t>09 May 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.3758</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.3502</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.3758</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>24 Apr 2026</t>
+          <t>08 May 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>23 Apr 2026</t>
+          <t>07 May 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1803,34 +1803,34 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>22 Apr 2026</t>
+          <t>06 May 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1840,177 +1840,177 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>21 Apr 2026</t>
+          <t>30 Apr 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20 Apr 2026</t>
+          <t>29 Apr 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.3732</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>16 Apr 2026</t>
+          <t>27 Apr 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3502</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>24 Apr 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2020,22 +2020,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2047,32 +2047,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>23 Apr 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>1.32</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1.37</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2084,44 +2084,44 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13 Apr 2026</t>
+          <t>22 Apr 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10 Apr 2026</t>
+          <t>21 Apr 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2141,29 +2141,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>20 Apr 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.2992</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2178,29 +2178,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2215,436 +2215,436 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07 Apr 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>1.35</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>1.35</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.2992</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2669,51 +2669,51 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.311</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2723,76 +2723,76 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>1.5</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2802,66 +2802,66 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1.4522</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2871,128 +2871,128 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3002,24 +3002,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3029,29 +3029,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3061,34 +3061,34 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3098,39 +3098,39 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3140,266 +3140,266 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3409,19 +3409,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3436,115 +3436,115 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1.5053</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1.5051</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>1.37</t>
@@ -3552,110 +3552,110 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1.5236</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="F86" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
           <t>1.55</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>1.32</t>
@@ -3663,24 +3663,24 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3690,81 +3690,81 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>1.5</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5053</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3774,44 +3774,44 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>1.64</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3823,17 +3823,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3843,34 +3843,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3880,140 +3880,140 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
           <t>1.63</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>1.55</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4028,145 +4028,145 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4176,76 +4176,76 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4255,19 +4255,19 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4277,318 +4277,577 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
           <t>1.57</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4173</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>12 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>09 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>08 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1.3456</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>07 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr">
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Fixing_Repo_Rate_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,192 +456,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26 Jun 2026</t>
+          <t>24 Jul 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25 Jun 2026</t>
+          <t>23 Jul 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.39</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24 Jun 2026</t>
+          <t>22 Jul 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.5461</t>
+          <t>1.3935</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23 Jun 2026</t>
+          <t>21 Jul 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22 Jun 2026</t>
+          <t>20 Jul 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>1.48</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18 Jun 2026</t>
+          <t>17 Jul 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -651,1127 +651,1127 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4348</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.4338</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17 Jun 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1.431</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>1.43</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16 Jun 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15 Jun 2026</t>
+          <t>14 Jul 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12 Jun 2026</t>
+          <t>13 Jul 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.399</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11 Jun 2026</t>
+          <t>10 Jul 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10 Jun 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09 Jun 2026</t>
+          <t>08 Jul 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08 Jun 2026</t>
+          <t>07 Jul 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05 Jun 2026</t>
+          <t>06 Jul 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>1.38</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04 Jun 2026</t>
+          <t>03 Jul 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3873</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>03 Jun 2026</t>
+          <t>02 Jul 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02 Jun 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01 Jun 2026</t>
+          <t>30 Jun 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>29 May 2026</t>
+          <t>29 Jun 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>26 Jun 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.3577</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>25 Jun 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.3639</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.51</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>24 Jun 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.3727</t>
+          <t>1.5461</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>23 Jun 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>22 Jun 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>18 Jun 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.3131</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>17 Jun 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.3092</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>16 Jun 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>15 Jun 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15 May 2026</t>
+          <t>12 Jun 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>11 Jun 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.443</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>10 Jun 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>09 Jun 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11 May 2026</t>
+          <t>08 Jun 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09 May 2026</t>
+          <t>05 Jun 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.3758</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.3758</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08 May 2026</t>
+          <t>04 Jun 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1781,14 +1781,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07 May 2026</t>
+          <t>03 Jun 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1798,86 +1798,86 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06 May 2026</t>
+          <t>02 Jun 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>30 Apr 2026</t>
+          <t>01 Jun 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1887,39 +1887,39 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>29 Apr 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1929,56 +1929,56 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.3732</t>
+          <t>1.3577</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>27 Apr 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1988,39 +1988,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.3502</t>
+          <t>1.3639</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>24 Apr 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2030,29 +2030,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.3727</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.394</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>23 Apr 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2062,54 +2062,54 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>22 Apr 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2121,64 +2121,64 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21 Apr 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.3131</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20 Apr 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2188,34 +2188,34 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3092</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2225,14 +2225,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.31</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16 Apr 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2242,34 +2242,34 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>15 May 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2279,108 +2279,108 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>13 Apr 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.31</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10 Apr 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2390,86 +2390,86 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>11 May 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.2992</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>1.33</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>09 May 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.3758</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2479,833 +2479,833 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.3758</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07 Apr 2026</t>
+          <t>08 May 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>07 May 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>06 May 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>30 Apr 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>1.38</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>29 Apr 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.3732</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>27 Apr 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.3502</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>24 Apr 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>23 Apr 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>22 Apr 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>21 Apr 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>20 Apr 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
           <t>1.4</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>1.4522</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.37</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.2992</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
           <t>1.4</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3330,34 +3330,34 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
           <t>1.42</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3367,118 +3367,118 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.311</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3490,44 +3490,44 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
           <t>1.5</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3537,747 +3537,747 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
           <t>1.5</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1.5518</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
           <t>1.56</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>1.5053</t>
-        </is>
-      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1.5051</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
           <t>1.49</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>1.5236</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4522</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
           <t>1.5</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
           <t>1.46</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4287,113 +4287,113 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1.4173</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5518</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4403,219 +4403,219 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1.5053</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
           <t>1.62</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1.5051</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
           <t>1.63</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5236</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4637,217 +4637,957 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1.3456</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
           <t>1.57</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>29 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>28 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>27 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>26 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>23 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>22 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>21 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1.4173</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>20 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>19 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>16 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>15 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>14 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>13 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>12 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>09 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>08 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1.3456</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>07 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
-      <c r="B121" t="inlineStr">
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
